--- a/assets/excel/bond-valuation-model-pfc.xlsx
+++ b/assets/excel/bond-valuation-model-pfc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCCB518-59EE-40A5-8FCE-94954AA3D7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A739FE-37F7-412A-B50E-4E500AFE7C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,7 +407,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Anvay:</t>
+          <t xml:space="preserve">Anvay:
+</t>
         </r>
         <r>
           <rPr>
@@ -416,9 +417,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-In the previous section, we compared Modified Duration (ModD) to a stock's Beta. Modified Duration assumes that a bond's price moves in a straight line when interest rates change.
-Interpretation: Look at Row 4 (-200 bps). Duration estimated that the bond's price would be ₹1,084.78. However, the actual price (shown in Column D) is ₹1,100.83.
+          <t>Look at Row 4 (-200 bps). Duration estimated that the bond's price would be ₹1,084.78. However, the actual price (shown in Column D) is ₹1,100.83.
 Why is there a difference of about ₹16?
 Because Duration is only a linear approximation. In reality, bond prices do not move in a straight line they move along a curve. This difference between the estimated price and the actual price is caused by that curvature. The next formula is designed to capture this effect and improve the accuracy of the price estimate.</t>
         </r>
@@ -434,7 +433,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Anvay:</t>
+          <t xml:space="preserve">Anvay:
+</t>
         </r>
         <r>
           <rPr>
@@ -443,9 +443,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-This formula corrects the error in the Duration estimate by adding the bond's Convexity, which captures the bond's curved price movement.
-Interpretation: Look again at Row 4 (-200 bps). The Duration + Convexity estimate gives a price of ₹1,095.89. This is much closer to the actual bond price of ₹1,100.83 than the Duration-only estimate.
+          <t>Look at Row 4 (-200 bps). The Duration + Convexity estimate gives a price of ₹1,095.89. This is much closer to the actual bond price of ₹1,100.83 than the Duration-only estimate.
 By including the bond's curve effect, Convexity makes the price estimate much more accurate.</t>
         </r>
       </text>
@@ -471,65 +469,10 @@
           </rPr>
           <t xml:space="preserve">
 This formula calculates the difference between the Duration only price estimate (₹1,084.78) and the Duration + Convexity estimate (₹1,095.89). In this case, the difference is ₹11.11.
-Interpretation (Key Insight):
 Experienced bond traders prefer bonds with high convexity. Notice that whether interest rates fall by 200 bps or rise by 200 bps, the Convexity Contribution remains positive (₹11.11).
 This is important because convexity works in your favor:
 When rates fall, it increases your gains.
-When rates rise, it reduces your losses.
-That is why convexity is often considered one of the most valuable features of a bond and a bond investor's best friend.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{5D495F0B-C41D-4B90-A073-7CD80C35E644}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Anvay:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Note: 0.31 INR variance between Manual DCF and Excel PRICE function is due to standard ACT/365 compounding conventions over partial periods.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C17" authorId="0" shapeId="0" xr:uid="{D7ED6EB3-D51E-40DE-801E-935FA336FCF1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Anvay:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Upar wali table (Yield Shock Table) bade jhatkon (macro shocks) ke liye banayi gayi hai—jaise RBI ne achanak 50 bps ya 100 bps rate badha diya.
-Lekin real market mein rates rozana 50 bps nahi hilte. Normal dino mein market 3 bps, 5 bps, ya 8 bps upar-neeche hota hai.Agar ek portfolio manager aapse pooche: "Bhai, aaj yield 10 bps gir gayi, batao mere ek bond pe kitna profit hua?"
-Toh aap upar wali badi table mein 10 bps nahi dhoondhenge (kyunki wahan -50 ke baad sidha 0 hai). Aap seedha is DV01 Reference ko dekhenge:
-DV01 = ₹0.645 (Yaani 1 bps hilne par ₹0.645 ka farq aayega).
-Mental Math: 0.645 * 10 = ₹6.45 ka profit.
-Summary: Yeh chota sa block isliye diya gaya hai taaki aane wale macro shocks (badi table) aur rozana ke micro shocks (DV01) dono ka analysis ek hi screen par, bina kisi aur sheet mein jaye, aasaani se kiya ja sake.</t>
+When rates rise, it reduces your losses.</t>
         </r>
       </text>
     </comment>
@@ -2477,7 +2420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
@@ -2486,80 +2429,706 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="13" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="24" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="17" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="41" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="18" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="13" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="15" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="44" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="45" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="50" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="49" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2569,235 +3138,14 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="13" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="174" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="1" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
@@ -2814,64 +3162,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2880,54 +3170,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="16" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="24" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="36" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
@@ -2940,269 +3186,30 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="23" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="17" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="41" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="39" fillId="18" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="39" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="39" fillId="13" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="40" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="15" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="40" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3216,76 +3223,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="44" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="45" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="50" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="49" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="52" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10449,319 +10391,319 @@
   <dimension ref="B1:N17"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="41.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="15" style="11" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="11" customWidth="1"/>
-    <col min="6" max="14" width="14" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="8.6640625" style="11"/>
+    <col min="1" max="1" width="2.33203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="41.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15" style="9" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="9" customWidth="1"/>
+    <col min="6" max="14" width="14" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="39" customHeight="1" thickBot="1">
-      <c r="B1" s="138" t="s">
+      <c r="B1" s="223" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="223"/>
     </row>
     <row r="2" spans="2:14">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="12"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="2:14" ht="36">
-      <c r="B3" s="215" t="s">
+      <c r="B3" s="193" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="215" t="s">
+      <c r="C3" s="193" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="194" t="s">
         <v>246</v>
       </c>
-      <c r="E3" s="216" t="s">
+      <c r="E3" s="194" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="217" t="s">
+      <c r="F3" s="234" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="217" t="s">
+      <c r="G3" s="235"/>
+      <c r="H3" s="235"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="234" t="s">
         <v>243</v>
       </c>
-      <c r="L3" s="218"/>
-      <c r="M3" s="218"/>
-      <c r="N3" s="219"/>
+      <c r="L3" s="235"/>
+      <c r="M3" s="235"/>
+      <c r="N3" s="236"/>
     </row>
     <row r="4" spans="2:14" ht="69.599999999999994" customHeight="1">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="207" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="195" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="220">
+      <c r="D4" s="195">
         <v>1</v>
       </c>
-      <c r="E4" s="221">
+      <c r="E4" s="196">
         <v>0.1</v>
       </c>
-      <c r="F4" s="236" t="s">
+      <c r="F4" s="232" t="s">
         <v>193</v>
       </c>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="237" t="s">
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="233" t="s">
         <v>194</v>
       </c>
-      <c r="L4" s="237"/>
-      <c r="M4" s="237"/>
-      <c r="N4" s="237"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="233"/>
+      <c r="N4" s="233"/>
     </row>
     <row r="5" spans="2:14" ht="65.400000000000006" customHeight="1">
-      <c r="B5" s="235" t="s">
+      <c r="B5" s="207" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="197" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="222">
+      <c r="D5" s="197">
         <v>4</v>
       </c>
-      <c r="E5" s="223">
+      <c r="E5" s="198">
         <v>0.2</v>
       </c>
-      <c r="F5" s="236" t="s">
+      <c r="F5" s="232" t="s">
         <v>195</v>
       </c>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="237" t="s">
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="233" t="s">
         <v>196</v>
       </c>
-      <c r="L5" s="237"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="237"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="233"/>
+      <c r="N5" s="233"/>
     </row>
     <row r="6" spans="2:14" ht="64.8" customHeight="1">
-      <c r="B6" s="235" t="s">
+      <c r="B6" s="207" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="224" t="s">
+      <c r="C6" s="199" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="224">
+      <c r="D6" s="199">
         <v>3</v>
       </c>
-      <c r="E6" s="225">
+      <c r="E6" s="200">
         <v>0.1</v>
       </c>
-      <c r="F6" s="236" t="s">
+      <c r="F6" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="237" t="s">
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="233" t="s">
         <v>198</v>
       </c>
-      <c r="L6" s="237"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="237"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="233"/>
     </row>
     <row r="7" spans="2:14" ht="61.2" customHeight="1">
-      <c r="B7" s="235" t="s">
+      <c r="B7" s="207" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="226" t="s">
+      <c r="C7" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="226">
+      <c r="D7" s="201">
         <v>2</v>
       </c>
-      <c r="E7" s="227">
+      <c r="E7" s="202">
         <v>0.05</v>
       </c>
-      <c r="F7" s="236" t="s">
+      <c r="F7" s="232" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="237" t="s">
+      <c r="G7" s="232"/>
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="233" t="s">
         <v>200</v>
       </c>
-      <c r="L7" s="237"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="237"/>
+      <c r="L7" s="233"/>
+      <c r="M7" s="233"/>
+      <c r="N7" s="233"/>
     </row>
     <row r="8" spans="2:14" ht="44.4" customHeight="1">
-      <c r="B8" s="235" t="s">
+      <c r="B8" s="207" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="226" t="s">
+      <c r="C8" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="D8" s="226">
+      <c r="D8" s="201">
         <v>2</v>
       </c>
-      <c r="E8" s="227">
+      <c r="E8" s="202">
         <v>0.05</v>
       </c>
-      <c r="F8" s="236" t="s">
+      <c r="F8" s="232" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="237" t="s">
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="L8" s="237"/>
-      <c r="M8" s="237"/>
-      <c r="N8" s="237"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
     </row>
     <row r="9" spans="2:14" ht="78" customHeight="1">
-      <c r="B9" s="235" t="s">
+      <c r="B9" s="207" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="224" t="s">
+      <c r="C9" s="199" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="224">
+      <c r="D9" s="199">
         <v>3</v>
       </c>
-      <c r="E9" s="225">
+      <c r="E9" s="200">
         <v>0.15</v>
       </c>
-      <c r="F9" s="236" t="s">
+      <c r="F9" s="232" t="s">
         <v>203</v>
       </c>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="237" t="s">
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="233" t="s">
         <v>204</v>
       </c>
-      <c r="L9" s="237"/>
-      <c r="M9" s="237"/>
-      <c r="N9" s="237"/>
+      <c r="L9" s="233"/>
+      <c r="M9" s="233"/>
+      <c r="N9" s="233"/>
     </row>
     <row r="10" spans="2:14" ht="69.599999999999994" customHeight="1">
-      <c r="B10" s="235" t="s">
+      <c r="B10" s="207" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="224" t="s">
+      <c r="C10" s="199" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="224">
+      <c r="D10" s="199">
         <v>3</v>
       </c>
-      <c r="E10" s="225">
+      <c r="E10" s="200">
         <v>0.2</v>
       </c>
-      <c r="F10" s="236" t="s">
+      <c r="F10" s="232" t="s">
         <v>206</v>
       </c>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="237" t="s">
+      <c r="G10" s="232"/>
+      <c r="H10" s="232"/>
+      <c r="I10" s="232"/>
+      <c r="J10" s="232"/>
+      <c r="K10" s="233" t="s">
         <v>205</v>
       </c>
-      <c r="L10" s="237"/>
-      <c r="M10" s="237"/>
-      <c r="N10" s="237"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="233"/>
+      <c r="N10" s="233"/>
     </row>
     <row r="11" spans="2:14" ht="69" customHeight="1">
-      <c r="B11" s="235" t="s">
+      <c r="B11" s="207" t="s">
         <v>184</v>
       </c>
-      <c r="C11" s="226" t="s">
+      <c r="C11" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="D11" s="226">
+      <c r="D11" s="201">
         <v>2</v>
       </c>
-      <c r="E11" s="227">
+      <c r="E11" s="202">
         <v>0.05</v>
       </c>
-      <c r="F11" s="236" t="s">
+      <c r="F11" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="237" t="s">
+      <c r="G11" s="232"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="233" t="s">
         <v>208</v>
       </c>
-      <c r="L11" s="237"/>
-      <c r="M11" s="237"/>
-      <c r="N11" s="237"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="233"/>
+      <c r="N11" s="233"/>
     </row>
     <row r="12" spans="2:14" ht="64.2" customHeight="1">
-      <c r="B12" s="235" t="s">
+      <c r="B12" s="207" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="224" t="s">
+      <c r="C12" s="199" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="224">
+      <c r="D12" s="199">
         <v>3</v>
       </c>
-      <c r="E12" s="225">
+      <c r="E12" s="200">
         <v>0.1</v>
       </c>
-      <c r="F12" s="236" t="s">
+      <c r="F12" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="G12" s="236"/>
-      <c r="H12" s="236"/>
-      <c r="I12" s="236"/>
-      <c r="J12" s="236"/>
-      <c r="K12" s="237" t="s">
+      <c r="G12" s="232"/>
+      <c r="H12" s="232"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="L12" s="237"/>
-      <c r="M12" s="237"/>
-      <c r="N12" s="237"/>
+      <c r="L12" s="233"/>
+      <c r="M12" s="233"/>
+      <c r="N12" s="233"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="E13" s="228"/>
+      <c r="E13" s="203"/>
     </row>
     <row r="14" spans="2:14" ht="7.5" customHeight="1"/>
     <row r="15" spans="2:14" ht="18">
@@ -10771,53 +10713,53 @@
       <c r="C15" s="230"/>
     </row>
     <row r="16" spans="2:14" ht="21">
-      <c r="B16" s="231" t="s">
+      <c r="B16" s="204" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="233">
+      <c r="C16" s="206">
         <f>SUMPRODUCT(D4:D12,E4:E12)</f>
         <v>2.8500000000000005</v>
       </c>
-      <c r="D16" s="234" t="str">
+      <c r="D16" s="231" t="str">
         <f>IF(C16&lt;2,"LOW RISK",IF(C16&lt;3,"LOW-MODERATE RISK",IF(C16&lt;3.5,"MODERATE RISK",IF(C16&lt;4.25,"MODERATE-HIGH RISK","HIGH RISK"))))</f>
         <v>LOW-MODERATE RISK</v>
       </c>
-      <c r="E16" s="234"/>
-      <c r="F16" s="234"/>
-      <c r="G16" s="234"/>
-      <c r="H16" s="234"/>
+      <c r="E16" s="231"/>
+      <c r="F16" s="231"/>
+      <c r="G16" s="231"/>
+      <c r="H16" s="231"/>
     </row>
     <row r="17" spans="2:2" ht="21" customHeight="1">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="205" t="s">
         <v>248</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ix7yyiYneCZotPLawdf52uoaScw6NK1uValQ+pk8vg8eNUQJmN2n/g2jxSK7QHOvQ8LJuuXdAww5KqWT1YOYCw==" saltValue="JldIE5ZVZnisVio/fD9sNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="23">
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:N10"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="F11:J11"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="F12:J12"/>
     <mergeCell ref="K12:N12"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="0.85" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -10833,12 +10775,12 @@
   <dimension ref="A1:R42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="11" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="4.33203125" style="9" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="31.8" thickBot="1">
-      <c r="A1" s="94"/>
+      <c r="A1"/>
       <c r="B1" s="238" t="s">
         <v>253</v>
       </c>
@@ -10860,832 +10802,832 @@
       <c r="R1" s="238"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="94"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
+      <c r="A2"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
     </row>
     <row r="3" spans="1:18" ht="21">
-      <c r="A3" s="94"/>
-      <c r="B3" s="239" t="s">
+      <c r="A3"/>
+      <c r="B3" s="237" t="s">
         <v>250</v>
       </c>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="239"/>
-      <c r="I3" s="239"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="239" t="s">
+      <c r="C3" s="237"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="237"/>
+      <c r="H3" s="237"/>
+      <c r="I3" s="237"/>
+      <c r="J3"/>
+      <c r="K3" s="237" t="s">
         <v>251</v>
       </c>
-      <c r="L3" s="239"/>
-      <c r="M3" s="239"/>
-      <c r="N3" s="239"/>
-      <c r="O3" s="239"/>
-      <c r="P3" s="239"/>
-      <c r="Q3" s="239"/>
-      <c r="R3" s="239"/>
+      <c r="L3" s="237"/>
+      <c r="M3" s="237"/>
+      <c r="N3" s="237"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="237"/>
+      <c r="Q3" s="237"/>
+      <c r="R3" s="237"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="94"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="94"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="94"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94"/>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="94"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="94"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="94"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="94"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94"/>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="94"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="94"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="94"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94"/>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="94"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="94"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="94"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="94"/>
-      <c r="O14" s="94"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="94"/>
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="94"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="94"/>
-      <c r="O15" s="94"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="94"/>
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="94"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="94"/>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="94"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="94"/>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="94"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
     </row>
     <row r="19" spans="1:18" ht="2.4" customHeight="1">
-      <c r="A19" s="94"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="94"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="94"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+      <c r="R20"/>
     </row>
     <row r="21" spans="1:18" ht="21">
-      <c r="A21" s="94"/>
-      <c r="B21" s="239" t="s">
+      <c r="A21"/>
+      <c r="B21" s="237" t="s">
         <v>252</v>
       </c>
-      <c r="C21" s="239"/>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="239" t="s">
+      <c r="C21" s="237"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="237"/>
+      <c r="J21"/>
+      <c r="K21" s="237" t="s">
         <v>252</v>
       </c>
-      <c r="L21" s="239"/>
-      <c r="M21" s="239"/>
-      <c r="N21" s="239"/>
-      <c r="O21" s="239"/>
-      <c r="P21" s="239"/>
-      <c r="Q21" s="239"/>
-      <c r="R21" s="239"/>
+      <c r="L21" s="237"/>
+      <c r="M21" s="237"/>
+      <c r="N21" s="237"/>
+      <c r="O21" s="237"/>
+      <c r="P21" s="237"/>
+      <c r="Q21" s="237"/>
+      <c r="R21" s="237"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="94"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="94"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="94"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="94"/>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="94"/>
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="94"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="94"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
+      <c r="R24"/>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="94"/>
-      <c r="B25" s="94"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="94"/>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="94"/>
-      <c r="N25" s="94"/>
-      <c r="O25" s="94"/>
-      <c r="P25" s="94"/>
-      <c r="Q25" s="94"/>
-      <c r="R25" s="94"/>
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+      <c r="R25"/>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="94"/>
-      <c r="B26" s="94"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="94"/>
-      <c r="E26" s="94"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="94"/>
-      <c r="L26" s="94"/>
-      <c r="M26" s="94"/>
-      <c r="N26" s="94"/>
-      <c r="O26" s="94"/>
-      <c r="P26" s="94"/>
-      <c r="Q26" s="94"/>
-      <c r="R26" s="94"/>
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="94"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="94"/>
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="94"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="94"/>
-      <c r="O28" s="94"/>
-      <c r="P28" s="94"/>
-      <c r="Q28" s="94"/>
-      <c r="R28" s="94"/>
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="94"/>
-      <c r="B29" s="94"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="94"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="94"/>
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="94"/>
-      <c r="B30" s="94"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="94"/>
-      <c r="M30" s="94"/>
-      <c r="N30" s="94"/>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30"/>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="94"/>
-      <c r="B31" s="94"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="94"/>
-      <c r="O31" s="94"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="94"/>
-      <c r="R31" s="94"/>
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="94"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="94"/>
-      <c r="M32" s="94"/>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="94"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="94"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="94"/>
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="94"/>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="94"/>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="94"/>
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="94"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="94"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="94"/>
-      <c r="O35" s="94"/>
-      <c r="P35" s="94"/>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="94"/>
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="94"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="94"/>
-      <c r="K36" s="94"/>
-      <c r="L36" s="94"/>
-      <c r="M36" s="94"/>
-      <c r="N36" s="94"/>
-      <c r="O36" s="94"/>
-      <c r="P36" s="94"/>
-      <c r="Q36" s="94"/>
-      <c r="R36" s="94"/>
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="94"/>
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
-      <c r="K37" s="94"/>
-      <c r="L37" s="94"/>
-      <c r="M37" s="94"/>
-      <c r="N37" s="94"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="94"/>
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="94"/>
-      <c r="B38" s="94"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="94"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="94"/>
-      <c r="K38" s="94"/>
-      <c r="L38" s="94"/>
-      <c r="M38" s="94"/>
-      <c r="N38" s="94"/>
-      <c r="O38" s="94"/>
-      <c r="P38" s="94"/>
-      <c r="Q38" s="94"/>
-      <c r="R38" s="94"/>
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="94"/>
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="94"/>
-      <c r="M39" s="94"/>
-      <c r="N39" s="94"/>
-      <c r="O39" s="94"/>
-      <c r="P39" s="94"/>
-      <c r="Q39" s="94"/>
-      <c r="R39" s="94"/>
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="94"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
-      <c r="F40" s="94"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94"/>
-      <c r="M40" s="94"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="94"/>
-      <c r="P40" s="94"/>
-      <c r="Q40" s="94"/>
-      <c r="R40" s="94"/>
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="94"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
-      <c r="N41" s="94"/>
-      <c r="O41" s="94"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="94"/>
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="94"/>
-      <c r="B42" s="94"/>
-      <c r="C42" s="94"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="94"/>
-      <c r="J42" s="94"/>
-      <c r="K42" s="94"/>
-      <c r="L42" s="94"/>
-      <c r="M42" s="94"/>
-      <c r="N42" s="94"/>
-      <c r="O42" s="94"/>
-      <c r="P42" s="94"/>
-      <c r="Q42" s="94"/>
-      <c r="R42" s="94"/>
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7F2Cn1wN/ElVQPWZ0wzg99O42Y+e8zFyRIQrfz97zZxXfDYkzEcLAYEVOlujow7246H0s58NsKHKT0v27y3nsA==" saltValue="WNuZvgE+FSRZW+ctzwEdvA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -11711,222 +11653,222 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="30" style="9" customWidth="1"/>
-    <col min="3" max="3" width="55" style="9" customWidth="1"/>
-    <col min="4" max="4" width="3.6640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="47.5546875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="28.21875" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="9"/>
+    <col min="1" max="1" width="2.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="30" style="8" customWidth="1"/>
+    <col min="3" max="3" width="55" style="8" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="47.5546875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="28.21875" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36.6" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:6" s="11" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+    </row>
+    <row r="2" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A2" s="211"/>
+      <c r="B2" s="211"/>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="21">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="208" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="E4" s="13" t="s">
+      <c r="C4" s="209"/>
+      <c r="E4" s="208" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="1:6" s="11" customFormat="1" ht="20.399999999999999" customHeight="1">
-      <c r="B5" s="15" t="s">
+      <c r="F4" s="209"/>
+    </row>
+    <row r="5" spans="1:6" s="9" customFormat="1" ht="20.399999999999999" customHeight="1">
+      <c r="B5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="21" customHeight="1">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <v>46182</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="19">
         <f>Face_Value*Coupon_Rate/Coupon_Frequency</f>
         <v>71.5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21" customHeight="1">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="15">
         <v>1000</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="20">
         <f>YEARFRAC(Issue_Date,Maturity_Date,1)</f>
         <v>14.997946611909651</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21" customHeight="1">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="16">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="21">
         <f>YEARFRAC(Settlement_Date,Maturity_Date,1)</f>
         <v>9.6202090592334493</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="21" customHeight="1">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="17">
         <v>1</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="22">
         <f>C11-C6</f>
         <v>3514</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="14">
         <v>44218</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="23">
         <f>COUPPCD(Settlement_Date,Maturity_Date,1,3)</f>
         <v>46044</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="14">
         <v>49696</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>COUPNCD(Settlement_Date,Maturity_Date,1,3)</f>
         <v>46409</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="15">
         <v>1028.93</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="22">
         <f>C6-F10</f>
         <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="16">
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="24">
         <f>Face_Value*Coupon_Rate*Days_Accrued/365</f>
         <v>27.032876712328768</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21" customHeight="1">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="21" customHeight="1">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="18" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="21" customHeight="1">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="16">
         <v>6.9699999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="21" customHeight="1">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="16">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="21" customHeight="1">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="16">
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
@@ -11962,283 +11904,283 @@
   <dimension ref="B1:I39"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="34.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" style="9" customWidth="1"/>
-    <col min="4" max="4" width="5" style="11" customWidth="1"/>
-    <col min="5" max="5" width="30" style="11" customWidth="1"/>
-    <col min="6" max="6" width="41" style="11" customWidth="1"/>
-    <col min="7" max="7" width="5" style="11" customWidth="1"/>
-    <col min="8" max="9" width="8.6640625" style="11"/>
-    <col min="10" max="16384" width="8.6640625" style="9"/>
+    <col min="1" max="1" width="2.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5" style="9" customWidth="1"/>
+    <col min="5" max="5" width="30" style="9" customWidth="1"/>
+    <col min="6" max="6" width="41" style="9" customWidth="1"/>
+    <col min="7" max="7" width="5" style="9" customWidth="1"/>
+    <col min="8" max="9" width="8.6640625" style="9"/>
+    <col min="10" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="18" customHeight="1">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
     </row>
     <row r="2" spans="2:6" ht="22.8" customHeight="1" thickBot="1">
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
     </row>
     <row r="4" spans="2:6" ht="21">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="212" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="E4" s="31" t="s">
+      <c r="C4" s="212"/>
+      <c r="E4" s="212" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="212"/>
     </row>
     <row r="5" spans="2:6" ht="21" customHeight="1">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="30">
         <f>Settlement_Date</f>
         <v>46182</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="21" customHeight="1">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="31">
         <f>Overview!F8</f>
         <v>9.6202090592334493</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="21" customHeight="1">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="32">
         <f>Current_YTM</f>
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="21" customHeight="1">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="33">
         <f>Dirty_Price</f>
         <v>986.43288989282246</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="21" customHeight="1">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="33">
         <f>Accrued_Interest</f>
         <v>27.032876712328768</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="21" customHeight="1">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="33">
         <f>clean_Price</f>
         <v>959.40001318049372</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21" customHeight="1">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="27">
         <f>Face_Value</f>
         <v>1000</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="32">
         <f>Current_Yield</f>
         <v>7.4525744233597979E-2</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="21" customHeight="1">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="28">
         <f>Issue_Date</f>
         <v>44218</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="31">
         <f>Macaulay_Duration</f>
         <v>7.0408061438278695</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="21" customHeight="1">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="28">
         <f>Maturity_Date</f>
         <v>49696</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="31">
         <f>Modified_Duration</f>
         <v>6.5343908527404828</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="21" customHeight="1">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="36" t="str">
+      <c r="C14" s="29" t="str">
         <f>TEXT(Overview!F7,"0.00")&amp;" years"</f>
         <v>15.00 years</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="33">
         <f>Valuation!C23</f>
         <v>0.64457380525580188</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="21" customHeight="1">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="31">
         <f>Convexity</f>
         <v>57.891941278410044</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="21" customHeight="1">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="31">
         <f>(Overview!$C$13-Overview!C16)*10000</f>
         <v>78.000000000000014</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="21" customHeight="1">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="31">
         <f>(Overview!$C$13-Overview!C17)*10000</f>
         <v>25.000000000000021</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="21" customHeight="1">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="31">
         <f>(Overview!$C$13-Overview!C18)*10000</f>
         <v>-75.000000000000071</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="21" customHeight="1">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="21" customHeight="1">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="41" t="str">
+      <c r="C20" s="34" t="str">
         <f>Overview!C14</f>
         <v>ACT/365</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="26" t="s">
         <v>67</v>
       </c>
     </row>
@@ -12281,599 +12223,599 @@
   <dimension ref="B1:L22"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="16" style="11" customWidth="1"/>
-    <col min="4" max="8" width="14" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="16" style="11" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="11"/>
+    <col min="1" max="1" width="2.33203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16" style="9" customWidth="1"/>
+    <col min="4" max="8" width="14" style="9" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16" style="9" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="37.200000000000003" thickBot="1">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="2:12">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="12"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="2:12" ht="27.6">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="38" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="18" customHeight="1">
-      <c r="B4" s="46">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="40">
         <v>46409</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="50">
         <f>C4-Overview!$C$6</f>
         <v>227</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="51">
         <f>D4/365</f>
         <v>0.62191780821917808</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="52">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="52">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="52">
         <f>F4+G4</f>
         <v>71.5</v>
       </c>
-      <c r="I4" s="60">
+      <c r="I4" s="51">
         <f>1/(1+Overview!$C$13)^E4</f>
         <v>0.95463887759518196</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="52">
         <f>H4*I4</f>
         <v>68.256679748055504</v>
       </c>
-      <c r="K4" s="71">
+      <c r="K4" s="62">
         <f>E4*J4</f>
         <v>42.450044665229036</v>
       </c>
-      <c r="L4" s="72">
+      <c r="L4" s="63">
         <f>E4*(E4+1)*J4</f>
         <v>68.850483402234502</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" customHeight="1">
-      <c r="B5" s="48">
+      <c r="B5" s="41">
         <v>2</v>
       </c>
-      <c r="C5" s="49">
+      <c r="C5" s="42">
         <v>46774</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="53">
         <f>C5-Overview!$C$6</f>
         <v>592</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="54">
         <f t="shared" ref="E5:E13" si="0">D5/365</f>
         <v>1.6219178082191781</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="55">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G5" s="64">
+      <c r="G5" s="55">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H5" s="64">
+      <c r="H5" s="55">
         <f t="shared" ref="H5:H13" si="1">F5+G5</f>
         <v>71.5</v>
       </c>
-      <c r="I5" s="63">
+      <c r="I5" s="54">
         <f>1/(1+Overview!$C$13)^E5</f>
         <v>0.88597575646884641</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="55">
         <f t="shared" ref="J5:J12" si="2">H5*I5</f>
         <v>63.347266587522519</v>
       </c>
-      <c r="K5" s="73">
+      <c r="K5" s="64">
         <f t="shared" ref="K5:K13" si="3">E5*J5</f>
         <v>102.74405978031049</v>
       </c>
-      <c r="L5" s="74">
+      <c r="L5" s="65">
         <f t="shared" ref="L5:L12" si="4">E5*(E5+1)*J5</f>
         <v>269.38648002673187</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18" customHeight="1">
-      <c r="B6" s="50">
+      <c r="B6" s="43">
         <v>3</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="42">
         <v>47140</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="56">
         <f>C6-Overview!$C$6</f>
         <v>958</v>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="57">
         <f t="shared" si="0"/>
         <v>2.6246575342465754</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="58">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="58">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="58">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="57">
         <f>1/(1+Overview!$C$13)^E6</f>
         <v>0.82208314656155135</v>
       </c>
-      <c r="J6" s="67">
+      <c r="J6" s="58">
         <f t="shared" si="2"/>
         <v>58.778944979150921</v>
       </c>
-      <c r="K6" s="75">
+      <c r="K6" s="66">
         <f t="shared" si="3"/>
         <v>154.2746007945934</v>
       </c>
-      <c r="L6" s="74">
+      <c r="L6" s="65">
         <f t="shared" si="4"/>
         <v>559.19259411300561</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18" customHeight="1">
-      <c r="B7" s="48">
+      <c r="B7" s="41">
         <v>4</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="42">
         <v>47505</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="53">
         <f>C7-Overview!$C$6</f>
         <v>1323</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="54">
         <f t="shared" si="0"/>
         <v>3.6246575342465754</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="55">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="55">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="55">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I7" s="63">
+      <c r="I7" s="54">
         <f>1/(1+Overview!$C$13)^E7</f>
         <v>0.76295419634482742</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="55">
         <f t="shared" si="2"/>
         <v>54.551225038655161</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="64">
         <f t="shared" si="3"/>
         <v>197.72950883874185</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="65">
         <f t="shared" si="4"/>
         <v>914.43126279396222</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="18" customHeight="1">
-      <c r="B8" s="50">
+      <c r="B8" s="43">
         <v>5</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="42">
         <v>47870</v>
       </c>
-      <c r="D8" s="65">
+      <c r="D8" s="56">
         <f>C8-Overview!$C$6</f>
         <v>1688</v>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="57">
         <f t="shared" si="0"/>
         <v>4.624657534246575</v>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="58">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="58">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="58">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I8" s="66">
+      <c r="I8" s="57">
         <f>1/(1+Overview!$C$13)^E8</f>
         <v>0.70807814045923656</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="58">
         <f t="shared" si="2"/>
         <v>50.627587042835415</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="66">
         <f t="shared" si="3"/>
         <v>234.1352518583731</v>
       </c>
-      <c r="L8" s="74">
+      <c r="L8" s="65">
         <f t="shared" si="4"/>
         <v>1316.9306083979175</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18" customHeight="1">
-      <c r="B9" s="48">
+      <c r="B9" s="41">
         <v>6</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="42">
         <v>48235</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="53">
         <f>C9-Overview!$C$6</f>
         <v>2053</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="54">
         <f t="shared" si="0"/>
         <v>5.624657534246575</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="55">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G9" s="64">
+      <c r="G9" s="55">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="55">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="54">
         <f>1/(1+Overview!$C$13)^E9</f>
         <v>0.65714908627307345</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="55">
         <f t="shared" si="2"/>
         <v>46.986159668524749</v>
       </c>
-      <c r="K9" s="73">
+      <c r="K9" s="64">
         <f t="shared" si="3"/>
         <v>264.28105698488031</v>
       </c>
-      <c r="L9" s="74">
+      <c r="L9" s="65">
         <f t="shared" si="4"/>
         <v>1750.7714953135355</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18" customHeight="1">
-      <c r="B10" s="50">
+      <c r="B10" s="43">
         <v>7</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="42">
         <v>48601</v>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="56">
         <f>C10-Overview!$C$6</f>
         <v>2419</v>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="57">
         <f t="shared" si="0"/>
         <v>6.6273972602739724</v>
       </c>
-      <c r="F10" s="67">
+      <c r="F10" s="58">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G10" s="67">
+      <c r="G10" s="58">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="58">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I10" s="66">
+      <c r="I10" s="57">
         <f>1/(1+Overview!$C$13)^E10</f>
         <v>0.60975843261960938</v>
       </c>
-      <c r="J10" s="67">
+      <c r="J10" s="58">
         <f t="shared" si="2"/>
         <v>43.597727932302071</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="66">
         <f t="shared" si="3"/>
         <v>288.93946265270876</v>
       </c>
-      <c r="L10" s="74">
+      <c r="L10" s="65">
         <f t="shared" si="4"/>
         <v>2203.8560658223046</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18" customHeight="1">
-      <c r="B11" s="48">
+      <c r="B11" s="41">
         <v>8</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="42">
         <v>48966</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="53">
         <f>C11-Overview!$C$6</f>
         <v>2784</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="54">
         <f t="shared" si="0"/>
         <v>7.6273972602739724</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="55">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="55">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="55">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I11" s="63">
+      <c r="I11" s="54">
         <f>1/(1+Overview!$C$13)^E11</f>
         <v>0.56590109755880236</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="55">
         <f t="shared" si="2"/>
         <v>40.461928475454371</v>
       </c>
-      <c r="K11" s="73">
+      <c r="K11" s="64">
         <f t="shared" si="3"/>
         <v>308.6192023990821</v>
       </c>
-      <c r="L11" s="74">
+      <c r="L11" s="65">
         <f t="shared" si="4"/>
         <v>2662.58046124578</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1">
-      <c r="B12" s="50">
+      <c r="B12" s="43">
         <v>9</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="42">
         <v>49331</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="56">
         <f>C12-Overview!$C$6</f>
         <v>3149</v>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="57">
         <f t="shared" si="0"/>
         <v>8.6273972602739732</v>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="58">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G12" s="67">
+      <c r="G12" s="58">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H12" s="67">
+      <c r="H12" s="58">
         <f t="shared" si="1"/>
         <v>71.5</v>
       </c>
-      <c r="I12" s="66">
+      <c r="I12" s="57">
         <f>1/(1+Overview!$C$13)^E12</f>
         <v>0.52519823439332003</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="58">
         <f t="shared" si="2"/>
         <v>37.55167375912238</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="66">
         <f t="shared" si="3"/>
         <v>323.97320730815449</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="65">
         <f t="shared" si="4"/>
         <v>3119.0187684406983</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18" customHeight="1">
-      <c r="B13" s="51">
+      <c r="B13" s="44">
         <v>10</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="45">
         <v>49696</v>
       </c>
-      <c r="D13" s="68">
+      <c r="D13" s="59">
         <f>C13-Overview!$C$6</f>
         <v>3514</v>
       </c>
-      <c r="E13" s="69">
+      <c r="E13" s="60">
         <f t="shared" si="0"/>
         <v>9.6273972602739732</v>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="61">
         <f>Overview!$C$7*Overview!$C$8</f>
         <v>71.5</v>
       </c>
-      <c r="G13" s="70">
+      <c r="G13" s="61">
         <f>Overview!$C$7</f>
         <v>1000</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="61">
         <f t="shared" si="1"/>
         <v>1071.5</v>
       </c>
-      <c r="I13" s="69">
+      <c r="I13" s="60">
         <f>1/(1+Overview!$C$13)^E13</f>
         <v>0.48742295535342928</v>
       </c>
-      <c r="J13" s="70">
+      <c r="J13" s="61">
         <f>H13*I13</f>
         <v>522.27369666119944</v>
       </c>
-      <c r="K13" s="76">
+      <c r="K13" s="67">
         <f t="shared" si="3"/>
         <v>5028.1363563491914</v>
       </c>
-      <c r="L13" s="77">
+      <c r="L13" s="68">
         <f>E13*(E13+1)*J13</f>
         <v>53436.002537749358</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" customHeight="1">
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="78">
+      <c r="C14" s="215"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="69">
         <f>SUM(F4:F13)</f>
         <v>715</v>
       </c>
-      <c r="G14" s="78">
+      <c r="G14" s="69">
         <f>SUM(G4:G13)</f>
         <v>1000</v>
       </c>
-      <c r="H14" s="78">
+      <c r="H14" s="69">
         <f>SUM(H4:H13)</f>
         <v>1715</v>
       </c>
-      <c r="I14" s="54"/>
-      <c r="J14" s="78">
+      <c r="I14" s="46"/>
+      <c r="J14" s="69">
         <f>SUM(J4:J13)</f>
         <v>986.43288989282246</v>
       </c>
-      <c r="K14" s="79">
+      <c r="K14" s="70">
         <f>SUM(K4:K13)</f>
         <v>6945.2827516312645</v>
       </c>
-      <c r="L14" s="79">
+      <c r="L14" s="70">
         <f>SUM(L4:L13)</f>
         <v>66301.020757305523</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="7.5" customHeight="1"/>
     <row r="17" spans="2:7" ht="18" customHeight="1">
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="216" t="s">
         <v>221</v>
       </c>
-      <c r="C17" s="55"/>
+      <c r="C17" s="216"/>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="80">
+      <c r="C18" s="71">
         <f>SUM(J4:J13)</f>
         <v>986.43288989282246</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="80">
+      <c r="C19" s="71">
         <f>Accrued_Interest</f>
         <v>27.032876712328768</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="80">
+      <c r="C20" s="71">
         <f>C18-C19</f>
         <v>959.40001318049372</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="81" t="str">
+      <c r="C21" s="72" t="str">
         <f>IF(ROUND(C18,2)=ROUND(C19+C20,2),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="G21" s="57"/>
+      <c r="G21" s="48"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="E22" s="58"/>
+      <c r="E22" s="49"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kY1mbGYyvjlzyZg7A2A1BX5aw+As1VKH5DKDmNWA2ZcvRQXHUIWGVQQo82O2Nrr86pv9N9lnqdiIcaNiw2g5Hw==" saltValue="9x6DmoLxoaZPxf6hWv/cLw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -12903,358 +12845,358 @@
   <dimension ref="B1:I25"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="28" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16" style="9" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="9" customWidth="1"/>
-    <col min="7" max="7" width="5.109375" style="9" customWidth="1"/>
-    <col min="8" max="8" width="28.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="12" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="9"/>
+    <col min="1" max="1" width="2.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="28" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16" style="8" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="8" customWidth="1"/>
+    <col min="7" max="7" width="5.109375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="12" style="8" customWidth="1"/>
+    <col min="13" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="37.200000000000003" thickBot="1">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="2:9">
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="99"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="89"/>
     </row>
     <row r="3" spans="2:9" ht="19.8">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="103" t="s">
+      <c r="C3" s="91"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="104"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="105" t="s">
+      <c r="F3" s="218"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="219" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="106"/>
+      <c r="I3" s="220"/>
     </row>
     <row r="4" spans="2:9" ht="22.8" customHeight="1">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="107" t="s">
+      <c r="E4" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="109" t="s">
+      <c r="F4" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="108" t="s">
+      <c r="H4" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="108" t="s">
+      <c r="I4" s="94" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="84">
+      <c r="C5" s="75">
         <f>Face_Value</f>
         <v>1000</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="85">
+      <c r="F5" s="76">
         <f>PRICE(Settlement_Date,Maturity_Date,Coupon_Rate,Current_YTM,100,1,3)*Face_Value/100</f>
         <v>959.70656274504825</v>
       </c>
-      <c r="H5" s="110" t="s">
+      <c r="H5" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="86" t="str">
+      <c r="I5" s="77" t="str">
         <f>IF(ROUND(SUM('Cash Flows'!J4:J13),2)=ROUND(Dirty_Price,2),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B6" s="110" t="s">
+      <c r="B6" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="87">
+      <c r="C6" s="78">
         <f>Coupon_Rate</f>
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="E6" s="110" t="s">
+      <c r="E6" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="79">
         <f>YIELD(Settlement_Date,Maturity_Date,Coupon_Rate,clean_Price/Face_Value*100,100,1,3)</f>
         <v>7.7547578782356727E-2</v>
       </c>
-      <c r="H6" s="110" t="s">
+      <c r="H6" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="I6" s="86" t="str">
+      <c r="I6" s="77" t="str">
         <f>IF(ROUND(Dirty_Price,2)=ROUND(clean_Price+Accrued_Interest,2),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="87">
+      <c r="C7" s="78">
         <f>Current_YTM</f>
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="E7" s="110" t="s">
+      <c r="E7" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="80">
         <f>DURATION(Settlement_Date,Maturity_Date,Coupon_Rate,Current_YTM,1,3)</f>
         <v>7.0370988773559935</v>
       </c>
-      <c r="H7" s="110" t="s">
+      <c r="H7" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="86" t="str">
+      <c r="I7" s="77" t="str">
         <f>IF(C21&lt;C20,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="90">
+      <c r="C8" s="81">
         <f>Settlement_Date</f>
         <v>46182</v>
       </c>
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="91">
+      <c r="F8" s="82">
         <f>MDURATION(Settlement_Date,Maturity_Date,Coupon_Rate,Current_YTM,1,3)</f>
         <v>6.5309502342050987</v>
       </c>
-      <c r="H8" s="110" t="s">
+      <c r="H8" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="86" t="str">
+      <c r="I8" s="77" t="str">
         <f>IF(PRICE(Settlement_Date,Maturity_Date,Coupon_Rate,Current_YTM+0.001,100,1,3)&lt;PRICE(Settlement_Date,Maturity_Date,Coupon_Rate,Current_YTM-0.001,100,1,3),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="81">
         <f>Maturity_Date</f>
         <v>49696</v>
       </c>
-      <c r="E9" s="110" t="s">
+      <c r="E9" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="85">
+      <c r="F9" s="76">
         <f>Overview!C7*Overview!C8*Overview!F12/365</f>
         <v>27.032876712328768</v>
       </c>
-      <c r="H9" s="110" t="s">
+      <c r="H9" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="86" t="str">
+      <c r="I9" s="77" t="str">
         <f>IF(ROUND(SUM('Cash Flows'!G4:G13),2)=ROUND(Face_Value,2),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="18" customHeight="1">
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="83">
         <f>Remaining_Tenor</f>
         <v>9.6202090592334493</v>
       </c>
-      <c r="F10" s="111"/>
+      <c r="F10" s="97"/>
     </row>
     <row r="11" spans="2:9" ht="18" customHeight="1">
-      <c r="C11" s="112"/>
+      <c r="C11" s="98"/>
     </row>
     <row r="12" spans="2:9" ht="18" customHeight="1">
-      <c r="B12" s="113" t="s">
+      <c r="B12" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="93">
+      <c r="C12" s="84">
         <f>Dirty_Price</f>
         <v>986.43288989282246</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="2:9" ht="18" customHeight="1">
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="81">
         <f>Overview!F10</f>
         <v>46044</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="2:9" ht="18" customHeight="1">
-      <c r="B14" s="113" t="s">
+      <c r="B14" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="95">
+      <c r="C14" s="85">
         <f>Days_Accrued</f>
         <v>138</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="2:9" ht="18" customHeight="1">
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="99" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="93">
+      <c r="C15" s="84">
         <f>Accrued_Interest</f>
         <v>27.032876712328768</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="2:9" ht="18" customHeight="1">
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="84">
         <f>clean_Price</f>
         <v>959.40001318049372</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="2:6" ht="18" customHeight="1">
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
     </row>
     <row r="18" spans="2:6" ht="18" customHeight="1">
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="87">
+      <c r="C18" s="78">
         <f>Face_Value*Coupon_Rate/C16</f>
         <v>7.4525744233597979E-2</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="2:6" ht="18" customHeight="1">
-      <c r="B19" s="112"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="2:6" ht="18" customHeight="1">
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="96">
+      <c r="C20" s="86">
         <f>Total_Duration/Total_Present_Value</f>
         <v>7.0408061438278695</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" spans="2:6" ht="18" customHeight="1">
-      <c r="B21" s="113" t="s">
+      <c r="B21" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="92">
+      <c r="C21" s="83">
         <f>Macaulay_Duration/(1+Current_YTM)</f>
         <v>6.5343908527404828</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" spans="2:6" ht="18" customHeight="1">
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="93">
+      <c r="C22" s="84">
         <f>Modified_Duration*Dirty_Price/100</f>
         <v>64.457380525580191</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" spans="2:6" ht="18" customHeight="1">
-      <c r="B23" s="113" t="s">
+      <c r="B23" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="84">
         <f>Modified_Duration*Dirty_Price/10000</f>
         <v>0.64457380525580188</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" spans="2:6" ht="18" customHeight="1">
-      <c r="B24" s="113" t="s">
+      <c r="B24" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="93">
+      <c r="C24" s="84">
         <f>C23</f>
         <v>0.64457380525580188</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" spans="2:6" ht="15.6">
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="97">
+      <c r="C25" s="87">
         <f>'Cash Flows'!L14/((1+Current_YTM)^2*Dirty_Price)</f>
         <v>57.891941278410044</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="zzTVJsIfjsEFJ2L5noLHNiNdf9a6bUykuwN9fJh5ZTcrJhCit9+OyFrZF4unZWvJjjrjCHMMrCHf57A2hiOc0w==" saltValue="hUX0zKiNsukpgCOJoqPp9g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -13284,433 +13226,433 @@
   <dimension ref="B1:J18"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="115" customWidth="1"/>
-    <col min="2" max="2" width="21" style="115" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="115" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="115" customWidth="1"/>
-    <col min="5" max="7" width="14" style="115" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" style="115" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="115" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" style="115" customWidth="1"/>
-    <col min="11" max="16384" width="8.6640625" style="115"/>
+    <col min="1" max="1" width="2.33203125" style="101" customWidth="1"/>
+    <col min="2" max="2" width="21" style="101" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="101" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="101" customWidth="1"/>
+    <col min="5" max="7" width="14" style="101" customWidth="1"/>
+    <col min="8" max="8" width="20.5546875" style="101" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="101" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="101" customWidth="1"/>
+    <col min="11" max="16384" width="8.6640625" style="101"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="37.200000000000003" thickBot="1">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="12"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="37" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="117">
+      <c r="C4" s="103">
         <v>-200</v>
       </c>
-      <c r="D4" s="128">
+      <c r="D4" s="112">
         <f t="shared" ref="D4:D12" si="0">Current_YTM+C4/10000</f>
         <v>5.7499999999999996E-2</v>
       </c>
-      <c r="E4" s="129">
+      <c r="E4" s="113">
         <f t="shared" ref="E4:E12" si="1">PRICE(Settlement_Date,Maturity_Date,Coupon_Rate,D4,100,1,3)*Face_Value/100</f>
         <v>1100.8300794455672</v>
       </c>
-      <c r="F4" s="129">
+      <c r="F4" s="113">
         <f t="shared" ref="F4:F12" si="2">E4-clean_Price</f>
         <v>141.43006626507349</v>
       </c>
-      <c r="G4" s="128">
+      <c r="G4" s="112">
         <f t="shared" ref="G4:G12" si="3">F4/clean_Price</f>
         <v>0.14741511811764588</v>
       </c>
-      <c r="H4" s="129">
+      <c r="H4" s="113">
         <f t="shared" ref="H4:H12" si="4">clean_Price*(1-Modified_Duration*(C4/10000))</f>
         <v>1084.781906585408</v>
       </c>
-      <c r="I4" s="129">
+      <c r="I4" s="113">
         <f t="shared" ref="I4:I12" si="5">clean_Price*(1-Modified_Duration*(C4/10000)+0.5*Convexity*(C4/10000)^2)</f>
         <v>1095.890212430518</v>
       </c>
-      <c r="J4" s="129">
+      <c r="J4" s="113">
         <f>clean_Price*0.5*Convexity*(C4/10000)^2</f>
         <v>11.108305845110193</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="119">
+      <c r="C5" s="105">
         <v>-150</v>
       </c>
-      <c r="D5" s="130">
+      <c r="D5" s="114">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="E5" s="131">
+      <c r="E5" s="115">
         <f t="shared" si="1"/>
         <v>1063.1339543385971</v>
       </c>
-      <c r="F5" s="131">
+      <c r="F5" s="115">
         <f t="shared" si="2"/>
         <v>103.73394115810333</v>
       </c>
-      <c r="G5" s="130">
+      <c r="G5" s="114">
         <f t="shared" si="3"/>
         <v>0.10812376457471204</v>
       </c>
-      <c r="H5" s="132">
+      <c r="H5" s="116">
         <f t="shared" si="4"/>
         <v>1053.4364332341795</v>
       </c>
-      <c r="I5" s="131">
+      <c r="I5" s="115">
         <f t="shared" si="5"/>
         <v>1059.6848552720539</v>
       </c>
-      <c r="J5" s="131">
+      <c r="J5" s="115">
         <f t="shared" ref="J5:J11" si="6">clean_Price*0.5*Convexity*(C5/10000)^2</f>
         <v>6.2484220378744828</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B6" s="120" t="s">
+      <c r="B6" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="119">
+      <c r="C6" s="105">
         <v>-100</v>
       </c>
-      <c r="D6" s="130">
+      <c r="D6" s="114">
         <f t="shared" si="0"/>
         <v>6.7500000000000004E-2</v>
       </c>
-      <c r="E6" s="131">
+      <c r="E6" s="115">
         <f t="shared" si="1"/>
         <v>1027.1032607212655</v>
       </c>
-      <c r="F6" s="131">
+      <c r="F6" s="115">
         <f t="shared" si="2"/>
         <v>67.703247540771827</v>
       </c>
-      <c r="G6" s="130">
+      <c r="G6" s="114">
         <f t="shared" si="3"/>
         <v>7.0568320419685762E-2</v>
       </c>
-      <c r="H6" s="131">
+      <c r="H6" s="115">
         <f t="shared" si="4"/>
         <v>1022.0909598829509</v>
       </c>
-      <c r="I6" s="131">
+      <c r="I6" s="115">
         <f t="shared" si="5"/>
         <v>1024.8680363442284</v>
       </c>
-      <c r="J6" s="131">
+      <c r="J6" s="115">
         <f t="shared" si="6"/>
         <v>2.7770764612775483</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="119">
+      <c r="C7" s="105">
         <v>-50</v>
       </c>
-      <c r="D7" s="130">
+      <c r="D7" s="114">
         <f t="shared" si="0"/>
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="E7" s="131">
+      <c r="E7" s="115">
         <f t="shared" si="1"/>
         <v>992.65392724567471</v>
       </c>
-      <c r="F7" s="131">
+      <c r="F7" s="115">
         <f t="shared" si="2"/>
         <v>33.253914065180993</v>
       </c>
-      <c r="G7" s="130">
+      <c r="G7" s="114">
         <f t="shared" si="3"/>
         <v>3.4661156564863287E-2</v>
       </c>
-      <c r="H7" s="132">
+      <c r="H7" s="116">
         <f t="shared" si="4"/>
         <v>990.74548653172224</v>
       </c>
-      <c r="I7" s="131">
+      <c r="I7" s="115">
         <f t="shared" si="5"/>
         <v>991.43975564704169</v>
       </c>
-      <c r="J7" s="131">
+      <c r="J7" s="115">
         <f t="shared" si="6"/>
         <v>0.69426911531938706</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="121">
+      <c r="C8" s="107">
         <v>0</v>
       </c>
-      <c r="D8" s="133">
+      <c r="D8" s="117">
         <f t="shared" si="0"/>
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="E8" s="134">
+      <c r="E8" s="118">
         <f t="shared" si="1"/>
         <v>959.70656274504825</v>
       </c>
-      <c r="F8" s="134">
+      <c r="F8" s="118">
         <f t="shared" si="2"/>
         <v>0.30654956455452975</v>
       </c>
-      <c r="G8" s="133">
+      <c r="G8" s="117">
         <f t="shared" si="3"/>
         <v>3.1952216004072328E-4</v>
       </c>
-      <c r="H8" s="135">
+      <c r="H8" s="119">
         <f t="shared" si="4"/>
         <v>959.40001318049372</v>
       </c>
-      <c r="I8" s="134">
+      <c r="I8" s="118">
         <f t="shared" si="5"/>
         <v>959.40001318049372</v>
       </c>
-      <c r="J8" s="134">
+      <c r="J8" s="118">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="119">
+      <c r="C9" s="105">
         <v>50</v>
       </c>
-      <c r="D9" s="130">
+      <c r="D9" s="114">
         <f t="shared" si="0"/>
         <v>8.2500000000000004E-2</v>
       </c>
-      <c r="E9" s="131">
+      <c r="E9" s="115">
         <f t="shared" si="1"/>
         <v>928.18617347633608</v>
       </c>
-      <c r="F9" s="131">
+      <c r="F9" s="115">
         <f t="shared" si="2"/>
         <v>-31.213839704157635</v>
       </c>
-      <c r="G9" s="130">
+      <c r="G9" s="114">
         <f t="shared" si="3"/>
         <v>-3.2534750130637446E-2</v>
       </c>
-      <c r="H9" s="132">
+      <c r="H9" s="116">
         <f t="shared" si="4"/>
         <v>928.0545398292652</v>
       </c>
-      <c r="I9" s="131">
+      <c r="I9" s="115">
         <f t="shared" si="5"/>
         <v>928.74880894458454</v>
       </c>
-      <c r="J9" s="131">
+      <c r="J9" s="115">
         <f t="shared" si="6"/>
         <v>0.69426911531938706</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="106" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="119">
+      <c r="C10" s="105">
         <v>100</v>
       </c>
-      <c r="D10" s="130">
+      <c r="D10" s="114">
         <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="E10" s="131">
+      <c r="E10" s="115">
         <f t="shared" si="1"/>
         <v>898.02189872421377</v>
       </c>
-      <c r="F10" s="131">
+      <c r="F10" s="115">
         <f t="shared" si="2"/>
         <v>-61.378114456279945</v>
       </c>
-      <c r="G10" s="130">
+      <c r="G10" s="114">
         <f t="shared" si="3"/>
         <v>-6.3975519713415682E-2</v>
       </c>
-      <c r="H10" s="131">
+      <c r="H10" s="115">
         <f t="shared" si="4"/>
         <v>896.70906647803656</v>
       </c>
-      <c r="I10" s="131">
+      <c r="I10" s="115">
         <f t="shared" si="5"/>
         <v>899.48614293931416</v>
       </c>
-      <c r="J10" s="131">
+      <c r="J10" s="115">
         <f t="shared" si="6"/>
         <v>2.7770764612775483</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="119">
+      <c r="C11" s="105">
         <v>150</v>
       </c>
-      <c r="D11" s="130">
+      <c r="D11" s="114">
         <f t="shared" si="0"/>
         <v>9.2499999999999999E-2</v>
       </c>
-      <c r="E11" s="131">
+      <c r="E11" s="115">
         <f t="shared" si="1"/>
         <v>869.14676349361241</v>
       </c>
-      <c r="F11" s="131">
+      <c r="F11" s="115">
         <f t="shared" si="2"/>
         <v>-90.253249686881304</v>
       </c>
-      <c r="G11" s="130">
+      <c r="G11" s="114">
         <f t="shared" si="3"/>
         <v>-9.4072595837980041E-2</v>
       </c>
-      <c r="H11" s="132">
+      <c r="H11" s="116">
         <f t="shared" si="4"/>
         <v>865.36359312680804</v>
       </c>
-      <c r="I11" s="131">
+      <c r="I11" s="115">
         <f t="shared" si="5"/>
         <v>871.61201516468248</v>
       </c>
-      <c r="J11" s="131">
+      <c r="J11" s="115">
         <f t="shared" si="6"/>
         <v>6.2484220378744828</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="119">
+      <c r="C12" s="105">
         <v>200</v>
       </c>
-      <c r="D12" s="130">
+      <c r="D12" s="114">
         <f t="shared" si="0"/>
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="E12" s="131">
+      <c r="E12" s="115">
         <f t="shared" si="1"/>
         <v>841.49744711169933</v>
       </c>
-      <c r="F12" s="131">
+      <c r="F12" s="115">
         <f t="shared" si="2"/>
         <v>-117.90256606879439</v>
       </c>
-      <c r="G12" s="130">
+      <c r="G12" s="114">
         <f t="shared" si="3"/>
         <v>-0.1228919787878022</v>
       </c>
-      <c r="H12" s="131">
+      <c r="H12" s="115">
         <f t="shared" si="4"/>
         <v>834.01811977557929</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="115">
         <f t="shared" si="5"/>
         <v>845.12642562068959</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="115">
         <f>clean_Price*0.5*Convexity*(C12/10000)^2</f>
         <v>11.108305845110193</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="7.5" customHeight="1"/>
     <row r="15" spans="2:10" ht="18" customHeight="1">
-      <c r="B15" s="122" t="s">
+      <c r="B15" s="221" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="123"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" spans="2:10" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="B16" s="124" t="s">
+      <c r="C15" s="222"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="2:10" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="B16" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="109" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="136">
+      <c r="C17" s="120">
         <f>Valuation!C23</f>
         <v>0.64457380525580188</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="121">
         <f>Valuation!C21</f>
         <v>6.5343908527404828</v>
       </c>
-      <c r="D18" s="127"/>
+      <c r="D18" s="111"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zBw/rhIwQIQfHUKBqDLTWpowXKTpb+i2Qpx6hT4PpWN0zvjZl5MOjSEYbgE07rhTYpTukMPdPNqTbUZdBOwSnw==" saltValue="aYU81KDGWrF6yq0xHWTwsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vkAFh9Ye62T32J3DYzjcc9eVjR6p6s+Me7uwOq+PDdzB64Z34Y/9SgmbeGPuRZM1hDnNXr3urNS6ea0MR+vBNA==" saltValue="PnY1S+FZ8twteqshFzSAag==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B15:C15"/>
   </mergeCells>
@@ -13733,187 +13675,187 @@
   <dimension ref="B1:E16"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="139" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" style="139" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" style="139" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" style="139" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" style="139" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="139"/>
+    <col min="1" max="1" width="2.33203125" style="122" customWidth="1"/>
+    <col min="2" max="2" width="42.5546875" style="122" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="122" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" style="122" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="122" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="122"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="31.8" thickBot="1">
-      <c r="B1" s="138" t="s">
+      <c r="B1" s="223" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="2:5" ht="7.5" customHeight="1"/>
     <row r="4" spans="2:5" ht="18">
-      <c r="B4" s="140" t="s">
+      <c r="B4" s="224" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="142"/>
+      <c r="C4" s="225"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="226"/>
     </row>
     <row r="5" spans="2:5" ht="15.6">
-      <c r="B5" s="143" t="s">
+      <c r="B5" s="123" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="124" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="144" t="s">
+      <c r="D5" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="144" t="s">
+      <c r="E5" s="124" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18" customHeight="1">
-      <c r="B6" s="145" t="s">
+      <c r="B6" s="125" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="146">
+      <c r="C6" s="126">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="D6" s="147">
+      <c r="D6" s="127">
         <f>Current_YTM</f>
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="E6" s="146">
+      <c r="E6" s="126">
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="18" customHeight="1">
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="148">
+      <c r="C7" s="128">
         <f>Valuation!$C$16</f>
         <v>959.40001318049372</v>
       </c>
-      <c r="D7" s="148">
+      <c r="D7" s="128">
         <f>Valuation!$C$16</f>
         <v>959.40001318049372</v>
       </c>
-      <c r="E7" s="148">
+      <c r="E7" s="128">
         <f>Valuation!$C$16</f>
         <v>959.40001318049372</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="7.5" customHeight="1"/>
     <row r="10" spans="2:5" ht="21" customHeight="1">
-      <c r="B10" s="140" t="s">
+      <c r="B10" s="224" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="142"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="226"/>
     </row>
     <row r="11" spans="2:5" ht="15.6">
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="123" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="124" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="144" t="s">
+      <c r="D11" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="144" t="s">
+      <c r="E11" s="124" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="19.5" customHeight="1">
-      <c r="B12" s="145" t="s">
+      <c r="B12" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="149">
+      <c r="C12" s="129">
         <f>PRICE(Settlement_Date+365,Maturity_Date,Coupon_Rate,C6,100,1,3)*Face_Value/100</f>
         <v>1092.6547690065599</v>
       </c>
-      <c r="D12" s="149">
+      <c r="D12" s="129">
         <f>PRICE(Settlement_Date+365,Maturity_Date,Coupon_Rate,D6,100,1,3)*Face_Value/100</f>
         <v>962.63229687446528</v>
       </c>
-      <c r="E12" s="149">
+      <c r="E12" s="129">
         <f>PRICE(Settlement_Date+365,Maturity_Date,Coupon_Rate,E6,100,1,3)*Face_Value/100</f>
         <v>905.16029384256501</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="19.5" customHeight="1">
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="132">
+      <c r="C13" s="116">
         <f>Face_Value*Coupon_Rate</f>
         <v>71.5</v>
       </c>
-      <c r="D13" s="132">
+      <c r="D13" s="116">
         <f>Face_Value*Coupon_Rate</f>
         <v>71.5</v>
       </c>
-      <c r="E13" s="132">
+      <c r="E13" s="116">
         <f>Face_Value*Coupon_Rate</f>
         <v>71.5</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1">
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="131">
+      <c r="C14" s="115">
         <f>C12-clean_Price</f>
         <v>133.25475582606623</v>
       </c>
-      <c r="D14" s="131">
+      <c r="D14" s="115">
         <f>D12-clean_Price</f>
         <v>3.2322836939715671</v>
       </c>
-      <c r="E14" s="131">
+      <c r="E14" s="115">
         <f>E12-clean_Price</f>
         <v>-54.239719337928705</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="19.5" customHeight="1">
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="96" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="132">
+      <c r="C15" s="116">
         <f>C13+C14</f>
         <v>204.75475582606623</v>
       </c>
-      <c r="D15" s="132">
+      <c r="D15" s="116">
         <f t="shared" ref="D15:E15" si="0">D13+D14</f>
         <v>74.732283693971567</v>
       </c>
-      <c r="E15" s="132">
+      <c r="E15" s="116">
         <f t="shared" si="0"/>
         <v>17.260280662071295</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="19.5" customHeight="1">
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="96" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="130">
+      <c r="C16" s="114">
         <f>C15/clean_Price</f>
         <v>0.21341958829798904</v>
       </c>
-      <c r="D16" s="130">
+      <c r="D16" s="114">
         <f>D15/clean_Price</f>
         <v>7.7894812035938593E-2</v>
       </c>
-      <c r="E16" s="130">
+      <c r="E16" s="114">
         <f>E15/clean_Price</f>
         <v>1.7990702965337658E-2</v>
       </c>
@@ -13944,1045 +13886,1045 @@
   <dimension ref="B1:O44"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="139" customWidth="1"/>
-    <col min="2" max="2" width="42" style="139" customWidth="1"/>
-    <col min="3" max="8" width="17" style="139" customWidth="1"/>
-    <col min="9" max="11" width="12" style="139" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" style="139" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12" style="139" customWidth="1"/>
-    <col min="16" max="16384" width="8.6640625" style="139"/>
+    <col min="1" max="1" width="2.33203125" style="122" customWidth="1"/>
+    <col min="2" max="2" width="42" style="122" customWidth="1"/>
+    <col min="3" max="8" width="17" style="122" customWidth="1"/>
+    <col min="9" max="11" width="12" style="122" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" style="122" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12" style="122" customWidth="1"/>
+    <col min="16" max="16384" width="8.6640625" style="122"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="31.8" thickBot="1">
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="227" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
     </row>
     <row r="2" spans="2:15">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
     </row>
     <row r="3" spans="2:15" ht="18" customHeight="1">
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="C3" s="225"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="225"/>
+      <c r="F3" s="225"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="225"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1">
-      <c r="B4" s="143" t="s">
+      <c r="B4" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="151" t="s">
+      <c r="C4" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="151" t="s">
+      <c r="D4" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="151" t="s">
+      <c r="E4" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="152" t="s">
+      <c r="F4" s="131" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="151" t="s">
+      <c r="G4" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="144" t="s">
+      <c r="H4" s="124" t="s">
         <v>135</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" spans="2:15" ht="18" customHeight="1">
-      <c r="B5" s="153" t="s">
+      <c r="B5" s="132" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="154">
+      <c r="C5" s="133">
         <v>76262</v>
       </c>
-      <c r="D5" s="154">
+      <c r="D5" s="133">
         <v>77807</v>
       </c>
-      <c r="E5" s="154">
+      <c r="E5" s="133">
         <v>91508</v>
       </c>
-      <c r="F5" s="154">
+      <c r="F5" s="133">
         <v>107106</v>
       </c>
-      <c r="G5" s="154">
+      <c r="G5" s="133">
         <v>115444</v>
       </c>
-      <c r="H5" s="176">
+      <c r="H5" s="155">
         <f>_xlfn.RRI(4,C5,G5)</f>
         <v>0.10921515308097463</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="2:15" ht="18" customHeight="1">
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="177">
+      <c r="C6" s="133"/>
+      <c r="D6" s="156">
         <f>D5/C5-1</f>
         <v>2.0259106763525825E-2</v>
       </c>
-      <c r="E6" s="177">
+      <c r="E6" s="156">
         <f>E5/D5-1</f>
         <v>0.17608955492436418</v>
       </c>
-      <c r="F6" s="177">
+      <c r="F6" s="156">
         <f>F5/E5-1</f>
         <v>0.17045504218210428</v>
       </c>
-      <c r="G6" s="177">
+      <c r="G6" s="156">
         <f>G5/F5-1</f>
         <v>7.7848113084234338E-2</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="2:15" ht="18" customHeight="1">
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="134" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="156">
+      <c r="C7" s="135">
         <v>23338</v>
       </c>
-      <c r="D7" s="156">
+      <c r="D7" s="135">
         <v>26501</v>
       </c>
-      <c r="E7" s="156">
+      <c r="E7" s="135">
         <v>33573</v>
       </c>
-      <c r="F7" s="156">
+      <c r="F7" s="135">
         <v>38603</v>
       </c>
-      <c r="G7" s="156">
+      <c r="G7" s="135">
         <v>42848</v>
       </c>
-      <c r="H7" s="178">
+      <c r="H7" s="157">
         <f>_xlfn.RRI(4,C7,G7)</f>
         <v>0.16403685249973465</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" spans="2:15" ht="18" customHeight="1">
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="154"/>
-      <c r="D8" s="177">
+      <c r="C8" s="133"/>
+      <c r="D8" s="156">
         <f>D7/C7-1</f>
         <v>0.13553003684977294</v>
       </c>
-      <c r="E8" s="177">
+      <c r="E8" s="156">
         <f>E7/D7-1</f>
         <v>0.26685785442058796</v>
       </c>
-      <c r="F8" s="177">
+      <c r="F8" s="156">
         <f>F7/E7-1</f>
         <v>0.14982277425311996</v>
       </c>
-      <c r="G8" s="177">
+      <c r="G8" s="156">
         <f>G7/F7-1</f>
         <v>0.10996554671916692</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" spans="2:15" ht="18" customHeight="1">
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="134" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="156">
+      <c r="C9" s="135">
         <v>23382</v>
       </c>
-      <c r="D9" s="156">
+      <c r="D9" s="135">
         <v>26496</v>
       </c>
-      <c r="E9" s="156">
+      <c r="E9" s="135">
         <v>33588</v>
       </c>
-      <c r="F9" s="156">
+      <c r="F9" s="135">
         <v>38632</v>
       </c>
-      <c r="G9" s="156">
+      <c r="G9" s="135">
         <v>42850</v>
       </c>
-      <c r="H9" s="178">
+      <c r="H9" s="157">
         <f>_xlfn.RRI(4,C9,G9)</f>
         <v>0.16350242427645556</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
     </row>
     <row r="10" spans="2:15" ht="18" customHeight="1">
-      <c r="B10" s="153" t="s">
+      <c r="B10" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="154"/>
-      <c r="D10" s="177">
+      <c r="C10" s="133"/>
+      <c r="D10" s="156">
         <f>D9/C9-1</f>
         <v>0.13317936874518854</v>
       </c>
-      <c r="E10" s="177">
+      <c r="E10" s="156">
         <f>E9/D9-1</f>
         <v>0.26766304347826098</v>
       </c>
-      <c r="F10" s="177">
+      <c r="F10" s="156">
         <f>F9/E9-1</f>
         <v>0.15017268071930445</v>
       </c>
-      <c r="G10" s="177">
+      <c r="G10" s="156">
         <f>G9/F9-1</f>
         <v>0.1091840960861461</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
     </row>
     <row r="11" spans="2:15" ht="18" customHeight="1">
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="134" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="156">
+      <c r="C11" s="135">
         <v>18768</v>
       </c>
-      <c r="D11" s="156">
+      <c r="D11" s="135">
         <v>21179</v>
       </c>
-      <c r="E11" s="156">
+      <c r="E11" s="135">
         <v>26461</v>
       </c>
-      <c r="F11" s="156">
+      <c r="F11" s="135">
         <v>30514</v>
       </c>
-      <c r="G11" s="156">
+      <c r="G11" s="135">
         <v>33625</v>
       </c>
-      <c r="H11" s="178">
+      <c r="H11" s="157">
         <f>_xlfn.RRI(4,C11,G11)</f>
         <v>0.15694063387599844</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" spans="2:15" ht="18" customHeight="1">
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="154"/>
-      <c r="D12" s="177">
+      <c r="C12" s="133"/>
+      <c r="D12" s="156">
         <f>D11/C11-1</f>
         <v>0.12846334185848263</v>
       </c>
-      <c r="E12" s="177">
+      <c r="E12" s="156">
         <f>E11/D11-1</f>
         <v>0.24939798857358708</v>
       </c>
-      <c r="F12" s="177">
+      <c r="F12" s="156">
         <f>F11/E11-1</f>
         <v>0.15316881448169006</v>
       </c>
-      <c r="G12" s="177">
+      <c r="G12" s="156">
         <f>G11/F11-1</f>
         <v>0.10195320180900569</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" spans="2:15" ht="18" customHeight="1">
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="134" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="157">
+      <c r="C13" s="136">
         <v>42.47</v>
       </c>
-      <c r="D13" s="157">
+      <c r="D13" s="136">
         <v>48.15</v>
       </c>
-      <c r="E13" s="157">
+      <c r="E13" s="136">
         <v>59.88</v>
       </c>
-      <c r="F13" s="157">
+      <c r="F13" s="136">
         <v>69.67</v>
       </c>
-      <c r="G13" s="157">
+      <c r="G13" s="136">
         <v>78.489999999999995</v>
       </c>
-      <c r="H13" s="178">
+      <c r="H13" s="157">
         <f>_xlfn.RRI(4,C13,G13)</f>
         <v>0.16595829645305837</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="158" t="s">
+      <c r="B14" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="159"/>
-      <c r="D14" s="179">
+      <c r="C14" s="138"/>
+      <c r="D14" s="158">
         <f>D13/C13-1</f>
         <v>0.13374146456322111</v>
       </c>
-      <c r="E14" s="179">
+      <c r="E14" s="158">
         <f>E13/D13-1</f>
         <v>0.24361370716510922</v>
       </c>
-      <c r="F14" s="179">
+      <c r="F14" s="158">
         <f>F13/E13-1</f>
         <v>0.1634936539746159</v>
       </c>
-      <c r="G14" s="179">
+      <c r="G14" s="158">
         <f>G13/F13-1</f>
         <v>0.12659681354959074</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" spans="2:15" ht="18" customHeight="1">
-      <c r="B17" s="140" t="s">
+      <c r="B17" s="224" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
+      <c r="C17" s="225"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="225"/>
+      <c r="G17" s="225"/>
+      <c r="H17" s="225"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" spans="2:15" ht="15" customHeight="1">
-      <c r="B18" s="143" t="s">
+      <c r="B18" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="151" t="s">
+      <c r="C18" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="151" t="s">
+      <c r="D18" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="151" t="s">
+      <c r="E18" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="F18" s="152" t="s">
+      <c r="F18" s="131" t="s">
         <v>133</v>
       </c>
-      <c r="G18" s="151" t="s">
+      <c r="G18" s="130" t="s">
         <v>228</v>
       </c>
-      <c r="H18" s="151" t="s">
+      <c r="H18" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" spans="2:15" ht="18" customHeight="1">
-      <c r="B19" s="160" t="s">
+      <c r="B19" s="139" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="161">
+      <c r="C19" s="140">
         <v>2640</v>
       </c>
-      <c r="D19" s="162">
+      <c r="D19" s="141">
         <v>2640</v>
       </c>
-      <c r="E19" s="162">
+      <c r="E19" s="141">
         <v>3300</v>
       </c>
-      <c r="F19" s="162">
+      <c r="F19" s="141">
         <v>3300</v>
       </c>
-      <c r="G19" s="162">
+      <c r="G19" s="141">
         <v>3300</v>
       </c>
-      <c r="H19" s="180">
+      <c r="H19" s="159">
         <f>_xlfn.RRI(4,C19,G19)</f>
         <v>5.7371263440564091E-2</v>
       </c>
-      <c r="I19" s="163"/>
-      <c r="J19" s="164"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="2:15" ht="18" customHeight="1">
-      <c r="B20" s="165" t="s">
+      <c r="B20" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="166"/>
-      <c r="D20" s="181">
+      <c r="C20" s="145"/>
+      <c r="D20" s="160">
         <f>D19/C19-1</f>
         <v>0</v>
       </c>
-      <c r="E20" s="181">
+      <c r="E20" s="160">
         <f>E19/D19-1</f>
         <v>0.25</v>
       </c>
-      <c r="F20" s="181">
+      <c r="F20" s="160">
         <f>F19/E19-1</f>
         <v>0</v>
       </c>
-      <c r="G20" s="181">
+      <c r="G20" s="160">
         <f>G19/F19-1</f>
         <v>0</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="163"/>
-      <c r="J20" s="164"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="143"/>
     </row>
     <row r="21" spans="2:15" ht="18" customHeight="1">
-      <c r="B21" s="160" t="s">
+      <c r="B21" s="139" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="161">
+      <c r="C21" s="140">
         <v>69036</v>
       </c>
-      <c r="D21" s="162">
+      <c r="D21" s="141">
         <v>81518</v>
       </c>
-      <c r="E21" s="162">
+      <c r="E21" s="141">
         <v>97847</v>
       </c>
-      <c r="F21" s="162">
+      <c r="F21" s="141">
         <v>114438</v>
       </c>
-      <c r="G21" s="162">
+      <c r="G21" s="141">
         <v>129561</v>
       </c>
-      <c r="H21" s="180">
+      <c r="H21" s="159">
         <f>_xlfn.RRI(4,C21,G21)</f>
         <v>0.17044138084988258</v>
       </c>
-      <c r="J21" s="164"/>
+      <c r="J21" s="143"/>
     </row>
     <row r="22" spans="2:15" ht="18" customHeight="1">
-      <c r="B22" s="165" t="s">
+      <c r="B22" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="C22" s="166"/>
-      <c r="D22" s="181">
+      <c r="C22" s="145"/>
+      <c r="D22" s="160">
         <f>D21/C21-1</f>
         <v>0.18080421808911296</v>
       </c>
-      <c r="E22" s="181">
+      <c r="E22" s="160">
         <f>E21/D21-1</f>
         <v>0.20031158762481915</v>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="160">
         <f>F21/E21-1</f>
         <v>0.16956064059194453</v>
       </c>
-      <c r="G22" s="181">
+      <c r="G22" s="160">
         <f>G21/F21-1</f>
         <v>0.13215015991191748</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="J22" s="164"/>
-    </row>
-    <row r="23" spans="2:15" s="168" customFormat="1" ht="18" customHeight="1">
-      <c r="B23" s="167" t="s">
+      <c r="H22" s="9"/>
+      <c r="J22" s="143"/>
+    </row>
+    <row r="23" spans="2:15" s="147" customFormat="1" ht="18" customHeight="1">
+      <c r="B23" s="146" t="s">
         <v>227</v>
       </c>
-      <c r="C23" s="182">
+      <c r="C23" s="161">
         <f>C19+C21</f>
         <v>71676</v>
       </c>
-      <c r="D23" s="183">
+      <c r="D23" s="162">
         <f>D19+D21</f>
         <v>84158</v>
       </c>
-      <c r="E23" s="183">
+      <c r="E23" s="162">
         <f>E19+E21</f>
         <v>101147</v>
       </c>
-      <c r="F23" s="183">
+      <c r="F23" s="162">
         <f>F19+F21</f>
         <v>117738</v>
       </c>
-      <c r="G23" s="183">
+      <c r="G23" s="162">
         <f>G19+G21</f>
         <v>132861</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="J23" s="169"/>
+      <c r="H23" s="9"/>
+      <c r="J23" s="148"/>
     </row>
     <row r="24" spans="2:15" ht="18" customHeight="1">
-      <c r="B24" s="160" t="s">
+      <c r="B24" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="161">
+      <c r="C24" s="140">
         <v>660476</v>
       </c>
-      <c r="D24" s="162">
+      <c r="D24" s="141">
         <v>751158</v>
       </c>
-      <c r="E24" s="162">
+      <c r="E24" s="141">
         <v>861961</v>
       </c>
-      <c r="F24" s="162">
+      <c r="F24" s="141">
         <v>971758</v>
       </c>
-      <c r="G24" s="162">
+      <c r="G24" s="141">
         <v>1012503</v>
       </c>
-      <c r="H24" s="180">
+      <c r="H24" s="159">
         <f>_xlfn.RRI(4,C24,G24)</f>
         <v>0.11271724643286807</v>
       </c>
-      <c r="J24" s="164"/>
+      <c r="J24" s="143"/>
     </row>
     <row r="25" spans="2:15" ht="18" customHeight="1">
-      <c r="B25" s="165" t="s">
+      <c r="B25" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="C25" s="166"/>
-      <c r="D25" s="181">
+      <c r="C25" s="145"/>
+      <c r="D25" s="160">
         <f>D24/C24-1</f>
         <v>0.13729794875211221</v>
       </c>
-      <c r="E25" s="181">
+      <c r="E25" s="160">
         <f>E24/D24-1</f>
         <v>0.14750957854406122</v>
       </c>
-      <c r="F25" s="181">
+      <c r="F25" s="160">
         <f>F24/E24-1</f>
         <v>0.12738047313045486</v>
       </c>
-      <c r="G25" s="181">
+      <c r="G25" s="160">
         <f>G24/F24-1</f>
         <v>4.1929163433694461E-2</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="J25" s="164"/>
+      <c r="H25" s="9"/>
+      <c r="J25" s="143"/>
     </row>
     <row r="26" spans="2:15" ht="18" customHeight="1">
-      <c r="B26" s="160" t="s">
+      <c r="B26" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="161">
+      <c r="C26" s="140">
         <v>791000</v>
       </c>
-      <c r="D26" s="162">
+      <c r="D26" s="141">
         <v>896112</v>
       </c>
-      <c r="E26" s="162">
+      <c r="E26" s="141">
         <v>1038877</v>
       </c>
-      <c r="F26" s="162">
+      <c r="F26" s="141">
         <v>1178086</v>
       </c>
-      <c r="G26" s="162">
+      <c r="G26" s="141">
         <v>1244579</v>
       </c>
-      <c r="H26" s="180">
+      <c r="H26" s="159">
         <f>_xlfn.RRI(4,C26,G26)</f>
         <v>0.11998316935620124</v>
       </c>
-      <c r="J26" s="164"/>
+      <c r="J26" s="143"/>
     </row>
     <row r="27" spans="2:15" ht="18" customHeight="1">
-      <c r="B27" s="165" t="s">
+      <c r="B27" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="166"/>
-      <c r="D27" s="181">
+      <c r="C27" s="145"/>
+      <c r="D27" s="160">
         <f>D26/C26-1</f>
         <v>0.13288495575221249</v>
       </c>
-      <c r="E27" s="181">
+      <c r="E27" s="160">
         <f>E26/D26-1</f>
         <v>0.15931602299712533</v>
       </c>
-      <c r="F27" s="181">
+      <c r="F27" s="160">
         <f>F26/E26-1</f>
         <v>0.13399950138466821</v>
       </c>
-      <c r="G27" s="181">
+      <c r="G27" s="160">
         <f>G26/F26-1</f>
         <v>5.6441550107547256E-2</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="J27" s="164"/>
-    </row>
-    <row r="28" spans="2:15" s="168" customFormat="1" ht="18" customHeight="1">
-      <c r="B28" s="167" t="s">
+      <c r="H27" s="9"/>
+      <c r="J27" s="143"/>
+    </row>
+    <row r="28" spans="2:15" s="147" customFormat="1" ht="18" customHeight="1">
+      <c r="B28" s="146" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="184">
+      <c r="C28" s="163">
         <f>C24/C23</f>
         <v>9.2147441263463357</v>
       </c>
-      <c r="D28" s="185">
+      <c r="D28" s="164">
         <f>D24/D23</f>
         <v>8.9255685733976566</v>
       </c>
-      <c r="E28" s="185">
+      <c r="E28" s="164">
         <f>E24/E23</f>
         <v>8.5218642174261223</v>
       </c>
-      <c r="F28" s="185">
+      <c r="F28" s="164">
         <f>F24/F23</f>
         <v>8.2535629958042431</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="164">
         <f>G24/G23</f>
         <v>7.6207690744462262</v>
       </c>
-      <c r="H28" s="11"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" spans="2:15" ht="18" customHeight="1">
-      <c r="B29" s="160" t="s">
+      <c r="B29" s="139" t="s">
         <v>146</v>
       </c>
-      <c r="C29" s="161">
+      <c r="C29" s="140">
         <v>373388</v>
       </c>
-      <c r="D29" s="162">
+      <c r="D29" s="141">
         <v>432312</v>
       </c>
-      <c r="E29" s="162">
+      <c r="E29" s="141">
         <v>481353</v>
       </c>
-      <c r="F29" s="162">
+      <c r="F29" s="141">
         <v>543120</v>
       </c>
-      <c r="G29" s="162">
+      <c r="G29" s="141">
         <v>574018</v>
       </c>
-      <c r="H29" s="180">
+      <c r="H29" s="159">
         <f>_xlfn.RRI(4,C29,G29)</f>
         <v>0.11350273653509468</v>
       </c>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="170"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="181">
+      <c r="B30" s="149"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="160">
         <f>D29/C29-1</f>
         <v>0.15780903510557387</v>
       </c>
-      <c r="E30" s="181">
+      <c r="E30" s="160">
         <f>E29/D29-1</f>
         <v>0.11343890523510791</v>
       </c>
-      <c r="F30" s="181">
+      <c r="F30" s="160">
         <f>F29/E29-1</f>
         <v>0.12831954927049383</v>
       </c>
-      <c r="G30" s="181">
+      <c r="G30" s="160">
         <f>G29/F29-1</f>
         <v>5.6889821770511162E-2</v>
       </c>
-      <c r="H30" s="11"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="32" spans="2:15" ht="18" customHeight="1">
-      <c r="B32" s="140" t="s">
+      <c r="B32" s="224" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="141"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="141"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="141"/>
-      <c r="I32" s="141"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
     </row>
     <row r="33" spans="2:15" ht="15" customHeight="1">
-      <c r="B33" s="143" t="s">
+      <c r="B33" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="151" t="s">
+      <c r="C33" s="130" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="151" t="s">
+      <c r="D33" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="151" t="s">
+      <c r="E33" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="152" t="s">
+      <c r="F33" s="131" t="s">
         <v>132</v>
       </c>
-      <c r="G33" s="151" t="s">
+      <c r="G33" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="151" t="s">
+      <c r="H33" s="130" t="s">
         <v>149</v>
       </c>
-      <c r="I33" s="151" t="s">
+      <c r="I33" s="130" t="s">
         <v>150</v>
       </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
     </row>
     <row r="34" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B34" s="167" t="s">
+      <c r="B34" s="146" t="s">
         <v>230</v>
       </c>
-      <c r="C34" s="172">
+      <c r="C34" s="151">
         <v>7.3899999999999993E-2</v>
       </c>
-      <c r="D34" s="172">
+      <c r="D34" s="151">
         <v>5.6099999999999997E-2</v>
       </c>
-      <c r="E34" s="172">
+      <c r="E34" s="151">
         <v>3.9100000000000003E-2</v>
       </c>
-      <c r="F34" s="172">
+      <c r="F34" s="151">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="G34" s="172">
+      <c r="G34" s="151">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="H34" s="172">
+      <c r="H34" s="151">
         <v>1.26E-2</v>
       </c>
-      <c r="I34" s="186">
+      <c r="I34" s="165">
         <f t="shared" ref="I34:I40" si="0">AVERAGE(C34:H34)</f>
         <v>3.8550000000000001E-2</v>
       </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
     </row>
     <row r="35" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B35" s="167" t="s">
+      <c r="B35" s="146" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="172">
+      <c r="C35" s="151">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="D35" s="172">
+      <c r="D35" s="151">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="E35" s="172">
+      <c r="E35" s="151">
         <v>1.03E-2</v>
       </c>
-      <c r="F35" s="172">
+      <c r="F35" s="151">
         <v>8.5000000000000006E-3</v>
       </c>
-      <c r="G35" s="172">
+      <c r="G35" s="151">
         <v>3.8E-3</v>
       </c>
-      <c r="H35" s="172">
+      <c r="H35" s="151">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="I35" s="186">
+      <c r="I35" s="165">
         <f t="shared" si="0"/>
         <v>1.2350000000000002E-2</v>
       </c>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
     </row>
     <row r="36" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B36" s="167" t="s">
+      <c r="B36" s="146" t="s">
         <v>231</v>
       </c>
-      <c r="C36" s="172">
+      <c r="C36" s="151">
         <v>0.1883</v>
       </c>
-      <c r="D36" s="172">
+      <c r="D36" s="151">
         <v>0.2351</v>
       </c>
-      <c r="E36" s="172">
+      <c r="E36" s="151">
         <v>0.24399999999999999</v>
       </c>
-      <c r="F36" s="172">
+      <c r="F36" s="151">
         <v>0.25409999999999999</v>
       </c>
-      <c r="G36" s="172">
+      <c r="G36" s="151">
         <v>0.2208</v>
       </c>
-      <c r="H36" s="172">
+      <c r="H36" s="151">
         <v>0.22</v>
       </c>
-      <c r="I36" s="186">
+      <c r="I36" s="165">
         <f t="shared" si="0"/>
         <v>0.22705</v>
       </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
     </row>
     <row r="37" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B37" s="167" t="s">
+      <c r="B37" s="146" t="s">
         <v>232</v>
       </c>
-      <c r="C37" s="172">
+      <c r="C37" s="151">
         <v>0.21</v>
       </c>
-      <c r="D37" s="172">
+      <c r="D37" s="151">
         <v>0.21</v>
       </c>
-      <c r="E37" s="172">
+      <c r="E37" s="151">
         <v>0.2</v>
       </c>
-      <c r="F37" s="172">
+      <c r="F37" s="151">
         <v>0.21</v>
       </c>
-      <c r="G37" s="172">
+      <c r="G37" s="151">
         <v>0.21</v>
       </c>
-      <c r="H37" s="172">
+      <c r="H37" s="151">
         <v>0.21</v>
       </c>
-      <c r="I37" s="186">
+      <c r="I37" s="165">
         <f t="shared" si="0"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B38" s="167" t="s">
+      <c r="B38" s="146" t="s">
         <v>233</v>
       </c>
-      <c r="C38" s="172">
+      <c r="C38" s="151">
         <v>2.24E-2</v>
       </c>
-      <c r="D38" s="172">
+      <c r="D38" s="151">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="E38" s="172">
+      <c r="E38" s="151">
         <v>2.7699999999999999E-2</v>
       </c>
-      <c r="F38" s="172">
+      <c r="F38" s="151">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="G38" s="172">
+      <c r="G38" s="151">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H38" s="172">
+      <c r="H38" s="151">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="I38" s="186">
+      <c r="I38" s="165">
         <f t="shared" si="0"/>
         <v>2.8550000000000002E-2</v>
       </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
     </row>
     <row r="39" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B39" s="167" t="s">
+      <c r="B39" s="146" t="s">
         <v>234</v>
       </c>
-      <c r="C39" s="173">
+      <c r="C39" s="152">
         <v>6.36</v>
       </c>
-      <c r="D39" s="173">
+      <c r="D39" s="152">
         <v>5.52</v>
       </c>
-      <c r="E39" s="173">
+      <c r="E39" s="152">
         <v>5.43</v>
       </c>
-      <c r="F39" s="173">
+      <c r="F39" s="152">
         <v>5.26</v>
       </c>
-      <c r="G39" s="173">
+      <c r="G39" s="152">
         <v>5.23</v>
       </c>
-      <c r="H39" s="173">
+      <c r="H39" s="152">
         <v>4.8499999999999996</v>
       </c>
-      <c r="I39" s="187">
+      <c r="I39" s="166">
         <f t="shared" si="0"/>
         <v>5.4416666666666664</v>
       </c>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
     </row>
     <row r="40" spans="2:15" ht="20.399999999999999" customHeight="1">
-      <c r="B40" s="167" t="s">
+      <c r="B40" s="146" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="172">
+      <c r="C40" s="151">
         <v>4.07E-2</v>
       </c>
-      <c r="D40" s="172">
+      <c r="D40" s="151">
         <v>4.2700000000000002E-2</v>
       </c>
-      <c r="E40" s="172">
+      <c r="E40" s="151">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="F40" s="172">
+      <c r="F40" s="151">
         <v>4.02E-2</v>
       </c>
-      <c r="G40" s="172">
+      <c r="G40" s="151">
         <v>4.4499999999999998E-2</v>
       </c>
-      <c r="H40" s="172">
+      <c r="H40" s="151">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="I40" s="186">
+      <c r="I40" s="165">
         <f t="shared" si="0"/>
         <v>4.2166666666666658E-2</v>
       </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
     </row>
     <row r="41" spans="2:15">
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-    </row>
-    <row r="42" spans="2:15" s="174" customFormat="1">
-      <c r="B42" s="174" t="s">
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+    </row>
+    <row r="42" spans="2:15" s="153" customFormat="1">
+      <c r="B42" s="153" t="s">
         <v>249</v>
       </c>
-      <c r="C42" s="175">
+      <c r="C42" s="154">
         <v>0.15</v>
       </c>
-      <c r="D42" s="188">
+      <c r="D42" s="167">
         <f>C42</f>
         <v>0.15</v>
       </c>
-      <c r="E42" s="188">
+      <c r="E42" s="167">
         <f t="shared" ref="E42:H42" si="1">D42</f>
         <v>0.15</v>
       </c>
-      <c r="F42" s="188">
+      <c r="F42" s="167">
         <f t="shared" si="1"/>
         <v>0.15</v>
       </c>
-      <c r="G42" s="188">
+      <c r="G42" s="167">
         <f t="shared" si="1"/>
         <v>0.15</v>
       </c>
-      <c r="H42" s="188">
+      <c r="H42" s="167">
         <f t="shared" si="1"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="43" spans="2:15">
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
     </row>
     <row r="44" spans="2:15">
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="+rav4wXUgIiLPvNiUioxIfSaWxCthvParDSNYjIDiSrbWwst1fvcg+p1zo37+IAeE/Gs80mEWFfe0ZHrMAf4Qg==" saltValue="oB/YHofimQJHAhtmb7ftrw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -15008,283 +14950,283 @@
   <dimension ref="B1:I17"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="139" customWidth="1"/>
-    <col min="2" max="2" width="30" style="139" customWidth="1"/>
-    <col min="3" max="3" width="12" style="139" customWidth="1"/>
-    <col min="4" max="4" width="14" style="139" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="139" customWidth="1"/>
-    <col min="6" max="6" width="14" style="139" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="139" customWidth="1"/>
-    <col min="8" max="8" width="18" style="139" customWidth="1"/>
-    <col min="9" max="9" width="16" style="139" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="139"/>
+    <col min="1" max="1" width="2.33203125" style="122" customWidth="1"/>
+    <col min="2" max="2" width="30" style="122" customWidth="1"/>
+    <col min="3" max="3" width="12" style="122" customWidth="1"/>
+    <col min="4" max="4" width="14" style="122" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="122" customWidth="1"/>
+    <col min="6" max="6" width="14" style="122" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="122" customWidth="1"/>
+    <col min="8" max="8" width="18" style="122" customWidth="1"/>
+    <col min="9" max="9" width="16" style="122" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="122"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="31.8" thickBot="1">
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="227" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
     </row>
     <row r="2" spans="2:9">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
     </row>
     <row r="3" spans="2:9" ht="7.5" customHeight="1"/>
     <row r="4" spans="2:9" ht="31.2">
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="168" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="168" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="189" t="s">
+      <c r="D4" s="168" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="189" t="s">
+      <c r="E4" s="168" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="190" t="s">
+      <c r="F4" s="169" t="s">
         <v>237</v>
       </c>
-      <c r="G4" s="190" t="s">
+      <c r="G4" s="169" t="s">
         <v>238</v>
       </c>
-      <c r="H4" s="190" t="s">
+      <c r="H4" s="169" t="s">
         <v>239</v>
       </c>
-      <c r="I4" s="190" t="s">
+      <c r="I4" s="169" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B5" s="191" t="s">
+      <c r="B5" s="170" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="171" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="192">
+      <c r="D5" s="171">
         <v>2035</v>
       </c>
-      <c r="E5" s="193">
+      <c r="E5" s="172">
         <v>6.4799999999999996E-2</v>
       </c>
-      <c r="F5" s="193">
+      <c r="F5" s="172">
         <v>6.9134000000000001E-2</v>
       </c>
-      <c r="G5" s="194" t="s">
+      <c r="G5" s="173" t="s">
         <v>241</v>
       </c>
-      <c r="H5" s="195" t="s">
+      <c r="H5" s="174" t="s">
         <v>241</v>
       </c>
-      <c r="I5" s="196" t="s">
+      <c r="I5" s="175" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B6" s="197" t="s">
+      <c r="B6" s="176" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="198" t="s">
+      <c r="C6" s="177" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="198" t="s">
+      <c r="D6" s="177" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="208">
+      <c r="E6" s="186">
         <f>Coupon_Rate</f>
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="F6" s="208">
+      <c r="F6" s="186">
         <f>Current_YTM</f>
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="G6" s="209">
+      <c r="G6" s="187">
         <f>(F6-$F$5)*10000</f>
         <v>83.659999999999982</v>
       </c>
-      <c r="H6" s="199">
+      <c r="H6" s="178">
         <v>0</v>
       </c>
-      <c r="I6" s="198" t="s">
+      <c r="I6" s="177" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B7" s="191" t="s">
+      <c r="B7" s="170" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="192" t="s">
+      <c r="C7" s="171" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="200" t="s">
+      <c r="D7" s="179" t="s">
         <v>211</v>
       </c>
-      <c r="E7" s="192" t="s">
+      <c r="E7" s="171" t="s">
         <v>212</v>
       </c>
-      <c r="F7" s="193">
+      <c r="F7" s="172">
         <v>7.3899999999999993E-2</v>
       </c>
-      <c r="G7" s="210">
+      <c r="G7" s="188">
         <f>(F7-$F$5)*10000</f>
         <v>47.659999999999926</v>
       </c>
-      <c r="H7" s="211">
+      <c r="H7" s="189">
         <f>(F7-F6)*10000</f>
         <v>-36.000000000000057</v>
       </c>
-      <c r="I7" s="212" t="str">
+      <c r="I7" s="190" t="str">
         <f>IF(F7&gt;F6,"Wider / Cheaper",IF(F7=F6,"PAR","Tighter / Richer"))</f>
         <v>Tighter / Richer</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B8" s="201" t="s">
+      <c r="B8" s="180" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="202" t="s">
+      <c r="C8" s="181" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="202" t="s">
+      <c r="D8" s="181" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="203">
+      <c r="E8" s="182">
         <v>0.05</v>
       </c>
-      <c r="F8" s="204">
+      <c r="F8" s="183">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="G8" s="210">
+      <c r="G8" s="188">
         <f>(F8-$F$5)*10000</f>
         <v>-178.34000000000003</v>
       </c>
-      <c r="H8" s="213">
+      <c r="H8" s="191">
         <f>(F8-F6)*10000</f>
         <v>-262</v>
       </c>
-      <c r="I8" s="214" t="str">
+      <c r="I8" s="192" t="str">
         <f>IF(F8&gt;F6,"Wider / Cheaper",IF(F8=F6,"PAR","Tighter / Richer"))</f>
         <v>Tighter / Richer</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B9" s="191" t="s">
+      <c r="B9" s="170" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="192" t="s">
+      <c r="C9" s="171" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="192" t="s">
+      <c r="D9" s="171" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="192" t="s">
+      <c r="E9" s="171" t="s">
         <v>213</v>
       </c>
-      <c r="F9" s="193">
+      <c r="F9" s="172">
         <v>6.3E-2</v>
       </c>
-      <c r="G9" s="210">
+      <c r="G9" s="188">
         <f t="shared" ref="G9" si="0">(F9-$F$5)*10000</f>
         <v>-61.34</v>
       </c>
-      <c r="H9" s="211">
+      <c r="H9" s="189">
         <f>(F9-F6)*10000</f>
         <v>-145</v>
       </c>
-      <c r="I9" s="212" t="str">
+      <c r="I9" s="190" t="str">
         <f>IF(F9&gt;F6,"Wider / Cheaper",IF(F9=F6,"PAR","Tighter / Richer"))</f>
         <v>Tighter / Richer</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="19.2" customHeight="1">
-      <c r="B10" s="201" t="s">
+      <c r="B10" s="180" t="s">
         <v>166</v>
       </c>
-      <c r="C10" s="202" t="s">
+      <c r="C10" s="181" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="202" t="s">
+      <c r="D10" s="181" t="s">
         <v>167</v>
       </c>
-      <c r="E10" s="202" t="s">
+      <c r="E10" s="181" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="204">
+      <c r="F10" s="183">
         <v>0.08</v>
       </c>
-      <c r="G10" s="210">
+      <c r="G10" s="188">
         <f>(F10-$F$5)*10000</f>
         <v>108.66000000000001</v>
       </c>
-      <c r="H10" s="213">
+      <c r="H10" s="191">
         <f>(F10-F6)*10000</f>
         <v>25.000000000000021</v>
       </c>
-      <c r="I10" s="214" t="str">
+      <c r="I10" s="192" t="str">
         <f>IF(F10&gt;F6,"Wider / Cheaper",IF(F10=F6,"PAR","Tighter / Richer"))</f>
         <v>Wider / Cheaper</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="7.5" customHeight="1"/>
     <row r="13" spans="2:9" ht="18" customHeight="1" thickBot="1">
-      <c r="B13" s="205" t="s">
+      <c r="B13" s="184" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-      <c r="F13" s="206"/>
-      <c r="G13" s="206"/>
-      <c r="H13" s="206"/>
-      <c r="I13" s="206"/>
-    </row>
-    <row r="14" spans="2:9" s="11" customFormat="1" ht="4.95" customHeight="1" thickTop="1"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="185"/>
+      <c r="F13" s="185"/>
+      <c r="G13" s="185"/>
+      <c r="H13" s="185"/>
+      <c r="I13" s="185"/>
+    </row>
+    <row r="14" spans="2:9" s="9" customFormat="1" ht="4.95" customHeight="1" thickTop="1"/>
     <row r="15" spans="2:9" ht="70.2" customHeight="1">
-      <c r="B15" s="207" t="s">
+      <c r="B15" s="228" t="s">
         <v>242</v>
       </c>
-      <c r="C15" s="207"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="207"/>
-      <c r="H15" s="207"/>
-      <c r="I15" s="207"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="228"/>
+      <c r="F15" s="228"/>
+      <c r="G15" s="228"/>
+      <c r="H15" s="228"/>
+      <c r="I15" s="228"/>
     </row>
     <row r="16" spans="2:9" ht="22.8" customHeight="1">
-      <c r="B16" s="207"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-      <c r="F16" s="207"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="207"/>
-      <c r="I16" s="207"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="228"/>
+      <c r="E16" s="228"/>
+      <c r="F16" s="228"/>
+      <c r="G16" s="228"/>
+      <c r="H16" s="228"/>
+      <c r="I16" s="228"/>
     </row>
     <row r="17" spans="2:9" ht="1.8" customHeight="1">
-      <c r="B17" s="207"/>
-      <c r="C17" s="207"/>
-      <c r="D17" s="207"/>
-      <c r="E17" s="207"/>
-      <c r="F17" s="207"/>
-      <c r="G17" s="207"/>
-      <c r="H17" s="207"/>
-      <c r="I17" s="207"/>
+      <c r="B17" s="228"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="228"/>
+      <c r="G17" s="228"/>
+      <c r="H17" s="228"/>
+      <c r="I17" s="228"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="qawfigAFpgxCis/ij57SnuvDZEMCwPmn6SvUORWxzAEKROjZy08b48rkccq4ef4Ls+Jb4YKQnOX8nkx7wZMXjg==" saltValue="a4vUSr15VIWa6OvIo0pimQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
